--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_29-09-2025.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_29-09-2025.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.99</t>
+          <t>£11.97</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.99</t>
+          <t>£11.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.99</t>
+          <t>£11.97</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -638,25 +638,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff615f81eb5+80197]
+	GetHandleVerifier [0x0x7ff615f81f10+80288]
+	(No symbol) [0x0x7ff615d002fa]
+	(No symbol) [0x0x7ff615d57cd7]
+	(No symbol) [0x0x7ff615d57f9c]
+	(No symbol) [0x0x7ff615daba87]
+	(No symbol) [0x0x7ff615d803bf]
+	(No symbol) [0x0x7ff615da87fb]
+	(No symbol) [0x0x7ff615d80153]
+	(No symbol) [0x0x7ff615d48b02]
+	(No symbol) [0x0x7ff615d498d3]
+	GetHandleVerifier [0x0x7ff61623e83d+2949837]
+	GetHandleVerifier [0x0x7ff616238c6a+2926330]
+	GetHandleVerifier [0x0x7ff6162586c7+3055959]
+	GetHandleVerifier [0x0x7ff615f9cfee+191102]
+	GetHandleVerifier [0x0x7ff615fa50af+224063]
+	GetHandleVerifier [0x0x7ff615f8af64+117236]
+	GetHandleVerifier [0x0x7ff615f8b119+117673]
+	GetHandleVerifier [0x0x7ff615f710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -696,17 +696,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£15.30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£15.30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£15.30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -739,25 +739,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff615f81eb5+80197]
+	GetHandleVerifier [0x0x7ff615f81f10+80288]
+	(No symbol) [0x0x7ff615d002fa]
+	(No symbol) [0x0x7ff615d57cd7]
+	(No symbol) [0x0x7ff615d57f9c]
+	(No symbol) [0x0x7ff615daba87]
+	(No symbol) [0x0x7ff615d803bf]
+	(No symbol) [0x0x7ff615da87fb]
+	(No symbol) [0x0x7ff615d80153]
+	(No symbol) [0x0x7ff615d48b02]
+	(No symbol) [0x0x7ff615d498d3]
+	GetHandleVerifier [0x0x7ff61623e83d+2949837]
+	GetHandleVerifier [0x0x7ff616238c6a+2926330]
+	GetHandleVerifier [0x0x7ff6162586c7+3055959]
+	GetHandleVerifier [0x0x7ff615f9cfee+191102]
+	GetHandleVerifier [0x0x7ff615fa50af+224063]
+	GetHandleVerifier [0x0x7ff615f8af64+117236]
+	GetHandleVerifier [0x0x7ff615f8b119+117673]
+	GetHandleVerifier [0x0x7ff615f710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -840,25 +840,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff615f81eb5+80197]
+	GetHandleVerifier [0x0x7ff615f81f10+80288]
+	(No symbol) [0x0x7ff615d002fa]
+	(No symbol) [0x0x7ff615d57cd7]
+	(No symbol) [0x0x7ff615d57f9c]
+	(No symbol) [0x0x7ff615daba87]
+	(No symbol) [0x0x7ff615d803bf]
+	(No symbol) [0x0x7ff615da87fb]
+	(No symbol) [0x0x7ff615d80153]
+	(No symbol) [0x0x7ff615d48b02]
+	(No symbol) [0x0x7ff615d498d3]
+	GetHandleVerifier [0x0x7ff61623e83d+2949837]
+	GetHandleVerifier [0x0x7ff616238c6a+2926330]
+	GetHandleVerifier [0x0x7ff6162586c7+3055959]
+	GetHandleVerifier [0x0x7ff615f9cfee+191102]
+	GetHandleVerifier [0x0x7ff615fa50af+224063]
+	GetHandleVerifier [0x0x7ff615f8af64+117236]
+	GetHandleVerifier [0x0x7ff615f8b119+117673]
+	GetHandleVerifier [0x0x7ff615f710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -941,25 +941,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff615f81eb5+80197]
+	GetHandleVerifier [0x0x7ff615f81f10+80288]
+	(No symbol) [0x0x7ff615d002fa]
+	(No symbol) [0x0x7ff615d57cd7]
+	(No symbol) [0x0x7ff615d57f9c]
+	(No symbol) [0x0x7ff615daba87]
+	(No symbol) [0x0x7ff615d803bf]
+	(No symbol) [0x0x7ff615da87fb]
+	(No symbol) [0x0x7ff615d80153]
+	(No symbol) [0x0x7ff615d48b02]
+	(No symbol) [0x0x7ff615d498d3]
+	GetHandleVerifier [0x0x7ff61623e83d+2949837]
+	GetHandleVerifier [0x0x7ff616238c6a+2926330]
+	GetHandleVerifier [0x0x7ff6162586c7+3055959]
+	GetHandleVerifier [0x0x7ff615f9cfee+191102]
+	GetHandleVerifier [0x0x7ff615fa50af+224063]
+	GetHandleVerifier [0x0x7ff615f8af64+117236]
+	GetHandleVerifier [0x0x7ff615f8b119+117673]
+	GetHandleVerifier [0x0x7ff615f710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -999,17 +999,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£21.70</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£21.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£21.75</t>
+          <t>£21.70</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1042,25 +1042,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff615f81eb5+80197]
+	GetHandleVerifier [0x0x7ff615f81f10+80288]
+	(No symbol) [0x0x7ff615d002fa]
+	(No symbol) [0x0x7ff615d57cd7]
+	(No symbol) [0x0x7ff615d57f9c]
+	(No symbol) [0x0x7ff615daba87]
+	(No symbol) [0x0x7ff615d803bf]
+	(No symbol) [0x0x7ff615da87fb]
+	(No symbol) [0x0x7ff615d80153]
+	(No symbol) [0x0x7ff615d48b02]
+	(No symbol) [0x0x7ff615d498d3]
+	GetHandleVerifier [0x0x7ff61623e83d+2949837]
+	GetHandleVerifier [0x0x7ff616238c6a+2926330]
+	GetHandleVerifier [0x0x7ff6162586c7+3055959]
+	GetHandleVerifier [0x0x7ff615f9cfee+191102]
+	GetHandleVerifier [0x0x7ff615fa50af+224063]
+	GetHandleVerifier [0x0x7ff615f8af64+117236]
+	GetHandleVerifier [0x0x7ff615f8b119+117673]
+	GetHandleVerifier [0x0x7ff615f710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1100,17 +1100,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£21.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£21.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£21.95</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1143,25 +1143,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff615f81eb5+80197]
+	GetHandleVerifier [0x0x7ff615f81f10+80288]
+	(No symbol) [0x0x7ff615d002fa]
+	(No symbol) [0x0x7ff615d57cd7]
+	(No symbol) [0x0x7ff615d57f9c]
+	(No symbol) [0x0x7ff615daba87]
+	(No symbol) [0x0x7ff615d803bf]
+	(No symbol) [0x0x7ff615da87fb]
+	(No symbol) [0x0x7ff615d80153]
+	(No symbol) [0x0x7ff615d48b02]
+	(No symbol) [0x0x7ff615d498d3]
+	GetHandleVerifier [0x0x7ff61623e83d+2949837]
+	GetHandleVerifier [0x0x7ff616238c6a+2926330]
+	GetHandleVerifier [0x0x7ff6162586c7+3055959]
+	GetHandleVerifier [0x0x7ff615f9cfee+191102]
+	GetHandleVerifier [0x0x7ff615fa50af+224063]
+	GetHandleVerifier [0x0x7ff615f8af64+117236]
+	GetHandleVerifier [0x0x7ff615f8b119+117673]
+	GetHandleVerifier [0x0x7ff615f710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1201,17 +1201,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1244,25 +1244,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff615f81eb5+80197]
+	GetHandleVerifier [0x0x7ff615f81f10+80288]
+	(No symbol) [0x0x7ff615d002fa]
+	(No symbol) [0x0x7ff615d57cd7]
+	(No symbol) [0x0x7ff615d57f9c]
+	(No symbol) [0x0x7ff615daba87]
+	(No symbol) [0x0x7ff615d803bf]
+	(No symbol) [0x0x7ff615da87fb]
+	(No symbol) [0x0x7ff615d80153]
+	(No symbol) [0x0x7ff615d48b02]
+	(No symbol) [0x0x7ff615d498d3]
+	GetHandleVerifier [0x0x7ff61623e83d+2949837]
+	GetHandleVerifier [0x0x7ff616238c6a+2926330]
+	GetHandleVerifier [0x0x7ff6162586c7+3055959]
+	GetHandleVerifier [0x0x7ff615f9cfee+191102]
+	GetHandleVerifier [0x0x7ff615fa50af+224063]
+	GetHandleVerifier [0x0x7ff615f8af64+117236]
+	GetHandleVerifier [0x0x7ff615f8b119+117673]
+	GetHandleVerifier [0x0x7ff615f710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£27.30</t>
+          <t>£27.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£27.30</t>
+          <t>£27.27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£27.30</t>
+          <t>£27.27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1345,25 +1345,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff615f81eb5+80197]
+	GetHandleVerifier [0x0x7ff615f81f10+80288]
+	(No symbol) [0x0x7ff615d002fa]
+	(No symbol) [0x0x7ff615d57cd7]
+	(No symbol) [0x0x7ff615d57f9c]
+	(No symbol) [0x0x7ff615daba87]
+	(No symbol) [0x0x7ff615d803bf]
+	(No symbol) [0x0x7ff615da87fb]
+	(No symbol) [0x0x7ff615d80153]
+	(No symbol) [0x0x7ff615d48b02]
+	(No symbol) [0x0x7ff615d498d3]
+	GetHandleVerifier [0x0x7ff61623e83d+2949837]
+	GetHandleVerifier [0x0x7ff616238c6a+2926330]
+	GetHandleVerifier [0x0x7ff6162586c7+3055959]
+	GetHandleVerifier [0x0x7ff615f9cfee+191102]
+	GetHandleVerifier [0x0x7ff615fa50af+224063]
+	GetHandleVerifier [0x0x7ff615f8af64+117236]
+	GetHandleVerifier [0x0x7ff615f8b119+117673]
+	GetHandleVerifier [0x0x7ff615f710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£26.85</t>
+          <t>£26.82</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.85</t>
+          <t>£26.82</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.85</t>
+          <t>£26.82</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff615f81eb5+80197]
+	GetHandleVerifier [0x0x7ff615f81f10+80288]
+	(No symbol) [0x0x7ff615d002fa]
+	(No symbol) [0x0x7ff615d57cd7]
+	(No symbol) [0x0x7ff615d57f9c]
+	(No symbol) [0x0x7ff615daba87]
+	(No symbol) [0x0x7ff615d803bf]
+	(No symbol) [0x0x7ff615da87fb]
+	(No symbol) [0x0x7ff615d80153]
+	(No symbol) [0x0x7ff615d48b02]
+	(No symbol) [0x0x7ff615d498d3]
+	GetHandleVerifier [0x0x7ff61623e83d+2949837]
+	GetHandleVerifier [0x0x7ff616238c6a+2926330]
+	GetHandleVerifier [0x0x7ff6162586c7+3055959]
+	GetHandleVerifier [0x0x7ff615f9cfee+191102]
+	GetHandleVerifier [0x0x7ff615fa50af+224063]
+	GetHandleVerifier [0x0x7ff615f8af64+117236]
+	GetHandleVerifier [0x0x7ff615f8b119+117673]
+	GetHandleVerifier [0x0x7ff615f710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1547,25 +1547,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff615f81eb5+80197]
+	GetHandleVerifier [0x0x7ff615f81f10+80288]
+	(No symbol) [0x0x7ff615d002fa]
+	(No symbol) [0x0x7ff615d57cd7]
+	(No symbol) [0x0x7ff615d57f9c]
+	(No symbol) [0x0x7ff615daba87]
+	(No symbol) [0x0x7ff615d803bf]
+	(No symbol) [0x0x7ff615da87fb]
+	(No symbol) [0x0x7ff615d80153]
+	(No symbol) [0x0x7ff615d48b02]
+	(No symbol) [0x0x7ff615d498d3]
+	GetHandleVerifier [0x0x7ff61623e83d+2949837]
+	GetHandleVerifier [0x0x7ff616238c6a+2926330]
+	GetHandleVerifier [0x0x7ff6162586c7+3055959]
+	GetHandleVerifier [0x0x7ff615f9cfee+191102]
+	GetHandleVerifier [0x0x7ff615fa50af+224063]
+	GetHandleVerifier [0x0x7ff615f8af64+117236]
+	GetHandleVerifier [0x0x7ff615f8b119+117673]
+	GetHandleVerifier [0x0x7ff615f710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1605,17 +1605,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£32.95</t>
+          <t>£32.92</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.95</t>
+          <t>£32.92</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£32.95</t>
+          <t>£32.92</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1648,25 +1648,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff615f81eb5+80197]
+	GetHandleVerifier [0x0x7ff615f81f10+80288]
+	(No symbol) [0x0x7ff615d002fa]
+	(No symbol) [0x0x7ff615d57cd7]
+	(No symbol) [0x0x7ff615d57f9c]
+	(No symbol) [0x0x7ff615daba87]
+	(No symbol) [0x0x7ff615d803bf]
+	(No symbol) [0x0x7ff615da87fb]
+	(No symbol) [0x0x7ff615d80153]
+	(No symbol) [0x0x7ff615d48b02]
+	(No symbol) [0x0x7ff615d498d3]
+	GetHandleVerifier [0x0x7ff61623e83d+2949837]
+	GetHandleVerifier [0x0x7ff616238c6a+2926330]
+	GetHandleVerifier [0x0x7ff6162586c7+3055959]
+	GetHandleVerifier [0x0x7ff615f9cfee+191102]
+	GetHandleVerifier [0x0x7ff615fa50af+224063]
+	GetHandleVerifier [0x0x7ff615f8af64+117236]
+	GetHandleVerifier [0x0x7ff615f8b119+117673]
+	GetHandleVerifier [0x0x7ff615f710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1783,17 +1783,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£40.20</t>
+          <t>£40.18</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£40.20</t>
+          <t>£40.18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£40.20</t>
+          <t>£40.18</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1826,25 +1826,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff615f81eb5+80197]
+	GetHandleVerifier [0x0x7ff615f81f10+80288]
+	(No symbol) [0x0x7ff615d002fa]
+	(No symbol) [0x0x7ff615d57cd7]
+	(No symbol) [0x0x7ff615d57f9c]
+	(No symbol) [0x0x7ff615daba87]
+	(No symbol) [0x0x7ff615d803bf]
+	(No symbol) [0x0x7ff615da87fb]
+	(No symbol) [0x0x7ff615d80153]
+	(No symbol) [0x0x7ff615d48b02]
+	(No symbol) [0x0x7ff615d498d3]
+	GetHandleVerifier [0x0x7ff61623e83d+2949837]
+	GetHandleVerifier [0x0x7ff616238c6a+2926330]
+	GetHandleVerifier [0x0x7ff6162586c7+3055959]
+	GetHandleVerifier [0x0x7ff615f9cfee+191102]
+	GetHandleVerifier [0x0x7ff615fa50af+224063]
+	GetHandleVerifier [0x0x7ff615f8af64+117236]
+	GetHandleVerifier [0x0x7ff615f8b119+117673]
+	GetHandleVerifier [0x0x7ff615f710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1884,17 +1884,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1927,25 +1927,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff615f81eb5+80197]
+	GetHandleVerifier [0x0x7ff615f81f10+80288]
+	(No symbol) [0x0x7ff615d002fa]
+	(No symbol) [0x0x7ff615d57cd7]
+	(No symbol) [0x0x7ff615d57f9c]
+	(No symbol) [0x0x7ff615daba87]
+	(No symbol) [0x0x7ff615d803bf]
+	(No symbol) [0x0x7ff615da87fb]
+	(No symbol) [0x0x7ff615d80153]
+	(No symbol) [0x0x7ff615d48b02]
+	(No symbol) [0x0x7ff615d498d3]
+	GetHandleVerifier [0x0x7ff61623e83d+2949837]
+	GetHandleVerifier [0x0x7ff616238c6a+2926330]
+	GetHandleVerifier [0x0x7ff6162586c7+3055959]
+	GetHandleVerifier [0x0x7ff615f9cfee+191102]
+	GetHandleVerifier [0x0x7ff615fa50af+224063]
+	GetHandleVerifier [0x0x7ff615f8af64+117236]
+	GetHandleVerifier [0x0x7ff615f8b119+117673]
+	GetHandleVerifier [0x0x7ff615f710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1985,17 +1985,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£40.92</t>
+          <t>£40.89</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£40.92</t>
+          <t>£40.89</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£40.92</t>
+          <t>£40.89</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2028,25 +2028,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff703161eb5+80197]
-	GetHandleVerifier [0x0x7ff703161f10+80288]
-	(No symbol) [0x0x7ff702ee02fa]
-	(No symbol) [0x0x7ff702f37cd7]
-	(No symbol) [0x0x7ff702f37f9c]
-	(No symbol) [0x0x7ff702f8ba87]
-	(No symbol) [0x0x7ff702f603bf]
-	(No symbol) [0x0x7ff702f887fb]
-	(No symbol) [0x0x7ff702f60153]
-	(No symbol) [0x0x7ff702f28b02]
-	(No symbol) [0x0x7ff702f298d3]
-	GetHandleVerifier [0x0x7ff70341e83d+2949837]
-	GetHandleVerifier [0x0x7ff703418c6a+2926330]
-	GetHandleVerifier [0x0x7ff7034386c7+3055959]
-	GetHandleVerifier [0x0x7ff70317cfee+191102]
-	GetHandleVerifier [0x0x7ff7031850af+224063]
-	GetHandleVerifier [0x0x7ff70316af64+117236]
-	GetHandleVerifier [0x0x7ff70316b119+117673]
-	GetHandleVerifier [0x0x7ff7031510a8+11064]
+	GetHandleVerifier [0x0x7ff615f81eb5+80197]
+	GetHandleVerifier [0x0x7ff615f81f10+80288]
+	(No symbol) [0x0x7ff615d002fa]
+	(No symbol) [0x0x7ff615d57cd7]
+	(No symbol) [0x0x7ff615d57f9c]
+	(No symbol) [0x0x7ff615daba87]
+	(No symbol) [0x0x7ff615d803bf]
+	(No symbol) [0x0x7ff615da87fb]
+	(No symbol) [0x0x7ff615d80153]
+	(No symbol) [0x0x7ff615d48b02]
+	(No symbol) [0x0x7ff615d498d3]
+	GetHandleVerifier [0x0x7ff61623e83d+2949837]
+	GetHandleVerifier [0x0x7ff616238c6a+2926330]
+	GetHandleVerifier [0x0x7ff6162586c7+3055959]
+	GetHandleVerifier [0x0x7ff615f9cfee+191102]
+	GetHandleVerifier [0x0x7ff615fa50af+224063]
+	GetHandleVerifier [0x0x7ff615f8af64+117236]
+	GetHandleVerifier [0x0x7ff615f8b119+117673]
+	GetHandleVerifier [0x0x7ff615f710a8+11064]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
